--- a/examples/sequence/NORT/result/trial_id_indexed_result_data.xlsx
+++ b/examples/sequence/NORT/result/trial_id_indexed_result_data.xlsx
@@ -613,10 +613,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.366666666666667</v>
+        <v>6.066666666666666</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="D2" t="n">
         <v>3.366666666666667</v>
@@ -731,13 +731,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.366666666666667</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.366666666666667</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>18.25269171231934</v>
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="C4" t="n">
-        <v>1.733333333333333</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>2.366666666666667</v>
+        <v>5.033333333333333</v>
       </c>
       <c r="E4" t="n">
         <v>13.78993694737438</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.266666666666667</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>1.266666666666667</v>
+        <v>3.733333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="E5" t="n">
         <v>21.12216029878254</v>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.033333333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>2.033333333333333</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="E6" t="n">
         <v>12.17196074127026</v>
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="E7" t="n">
         <v>15.08474240847554</v>
@@ -1321,13 +1321,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="E8" t="n">
         <v>6.517670393953853</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8.9</v>
+        <v>15.93333333333333</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>8.9</v>
+        <v>14.8</v>
       </c>
       <c r="E12" t="n">
         <v>11.23367511360938</v>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>10.76666666666667</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>10.76666666666667</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.566666666666667</v>
+        <v>4.966666666666667</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2.566666666666667</v>
+        <v>4.966666666666667</v>
       </c>
       <c r="E14" t="n">
         <v>8.900942817846355</v>
@@ -2147,13 +2147,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8.133333333333333</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.466666666666667</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="E15" t="n">
         <v>14.63439736558077</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.266666666666667</v>
+        <v>3.1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.366666666666667</v>
       </c>
       <c r="D16" t="n">
-        <v>1.266666666666667</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="E16" t="n">
         <v>15.49284365275271</v>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.766666666666667</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="C17" t="n">
-        <v>1.766666666666667</v>
+        <v>2.866666666666667</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2501,13 +2501,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.333333333333333</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.333333333333333</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="E18" t="n">
         <v>7.855035192833869</v>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1</v>
+        <v>4.466666666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.233333333333333</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1</v>
+        <v>3.233333333333333</v>
       </c>
       <c r="E19" t="n">
         <v>17.24806018866558</v>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E20" t="n">
         <v>17.26087035772821</v>
@@ -2855,13 +2855,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3.366666666666667</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3.366666666666667</v>
       </c>
       <c r="E21" t="n">
         <v>19.39888948414773</v>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.766666666666667</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="C22" t="n">
-        <v>2.766666666666667</v>
+        <v>4.633333333333334</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>9.539934977835332</v>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>7.366666666666666</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="E24" t="n">
         <v>8.497549795728572</v>
@@ -3327,13 +3327,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E25" t="n">
         <v>7.606574844586245</v>
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.133333333333333</v>
+        <v>5.966666666666667</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3.133333333333333</v>
+        <v>5.966666666666667</v>
       </c>
       <c r="E26" t="n">
         <v>11.2598914730234</v>
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.8</v>
+        <v>4.133333333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>1.8</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="E27" t="n">
         <v>12.29837942710513</v>
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.866666666666667</v>
+        <v>7.066666666666666</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="D28" t="n">
-        <v>3.866666666666667</v>
+        <v>4.966666666666667</v>
       </c>
       <c r="E28" t="n">
         <v>11.17286665986802</v>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.533333333333333</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="D29" t="n">
         <v>1.533333333333333</v>
@@ -3917,13 +3917,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.466666666666667</v>
+        <v>25.8</v>
       </c>
       <c r="C30" t="n">
-        <v>4.366666666666666</v>
+        <v>9.733333333333333</v>
       </c>
       <c r="D30" t="n">
-        <v>3.1</v>
+        <v>16.06666666666667</v>
       </c>
       <c r="E30" t="n">
         <v>14.81027258964444</v>
@@ -4153,13 +4153,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.633333333333334</v>
+        <v>10.5</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>4.033333333333333</v>
       </c>
       <c r="D32" t="n">
-        <v>4.633333333333334</v>
+        <v>6.466666666666667</v>
       </c>
       <c r="E32" t="n">
         <v>8.448107418352315</v>
@@ -4271,13 +4271,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="E33" t="n">
         <v>4.30708152701668</v>
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.566666666666667</v>
+        <v>7</v>
       </c>
       <c r="C34" t="n">
-        <v>1.433333333333333</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="D34" t="n">
-        <v>1.133333333333333</v>
+        <v>4.033333333333333</v>
       </c>
       <c r="E34" t="n">
         <v>5.166480194574468</v>
@@ -4507,13 +4507,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>8.933333333333334</v>
+        <v>29.23333333333333</v>
       </c>
       <c r="C35" t="n">
-        <v>1.833333333333333</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
-        <v>7.1</v>
+        <v>15.23333333333333</v>
       </c>
       <c r="E35" t="n">
         <v>10.20861756219588</v>
@@ -4625,13 +4625,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.733333333333333</v>
+        <v>6.2</v>
       </c>
       <c r="C36" t="n">
         <v>1.5</v>
       </c>
       <c r="D36" t="n">
-        <v>2.233333333333333</v>
+        <v>4.7</v>
       </c>
       <c r="E36" t="n">
         <v>11.33188335420018</v>
@@ -4743,13 +4743,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>8.1</v>
+        <v>20.2</v>
       </c>
       <c r="C37" t="n">
-        <v>2.666666666666667</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="D37" t="n">
-        <v>5.433333333333334</v>
+        <v>9.533333333333333</v>
       </c>
       <c r="E37" t="n">
         <v>12.86163471647796</v>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.766666666666667</v>
+        <v>2.8</v>
       </c>
       <c r="C40" t="n">
-        <v>2.766666666666667</v>
+        <v>2.8</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E41" t="n">
         <v>11.42875249722521</v>
@@ -5333,13 +5333,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>6.466666666666667</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>5.366666666666666</v>
       </c>
       <c r="E42" t="n">
         <v>15.59142944575703</v>
@@ -5569,13 +5569,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>5.366666666666666</v>
+        <v>11.9</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="D44" t="n">
-        <v>5.366666666666666</v>
+        <v>6.8</v>
       </c>
       <c r="E44" t="n">
         <v>13.35491225639722</v>
@@ -5687,13 +5687,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>7.466666666666667</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>5.733333333333333</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="E45" t="n">
         <v>18.65944768150593</v>
@@ -5805,13 +5805,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>4.466666666666667</v>
       </c>
       <c r="E46" t="n">
         <v>10.04549364525433</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>4.233333333333333</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="E47" t="n">
         <v>16.46365461523338</v>
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.966666666666667</v>
+        <v>10.13333333333333</v>
       </c>
       <c r="C49" t="n">
-        <v>3.766666666666667</v>
+        <v>5.6</v>
       </c>
       <c r="D49" t="n">
-        <v>2.2</v>
+        <v>4.533333333333333</v>
       </c>
       <c r="E49" t="n">
         <v>17.10319990740055</v>
@@ -6277,13 +6277,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E50" t="n">
         <v>20.54072544385875</v>
@@ -6395,13 +6395,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>3.066666666666667</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>1.566666666666667</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E51" t="n">
         <v>15.14526782479423</v>
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.1</v>
+        <v>11.86666666666667</v>
       </c>
       <c r="C52" t="n">
-        <v>4.1</v>
+        <v>10.8</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1.066666666666667</v>
       </c>
       <c r="E52" t="n">
         <v>16.93866353133281</v>
@@ -6631,13 +6631,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3.6</v>
+        <v>7.3</v>
       </c>
       <c r="C53" t="n">
-        <v>1.3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="D53" t="n">
-        <v>2.3</v>
+        <v>3.466666666666667</v>
       </c>
       <c r="E53" t="n">
         <v>12.92914538883419</v>
@@ -6965,24 +6965,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J2" t="n">
         <v>5.834681912963971</v>
@@ -7094,28 +7098,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6</v>
+        <v>17.36666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>1.233333333333333</v>
+        <v>10.03333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>2.366666666666667</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.133333333333333</v>
+        <v>2.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3148148148148148</v>
+        <v>0.1554702495201536</v>
       </c>
       <c r="G3" t="n">
-        <v>34.25925925925926</v>
+        <v>57.77351247600768</v>
       </c>
       <c r="H3" t="n">
-        <v>34.25925925925926</v>
+        <v>57.77351247600768</v>
       </c>
       <c r="I3" t="n">
-        <v>65.74074074074073</v>
+        <v>42.22648752399232</v>
       </c>
       <c r="J3" t="n">
         <v>17.06019112172024</v>
@@ -7227,28 +7231,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.933333333333333</v>
+        <v>7.266666666666667</v>
       </c>
       <c r="C4" t="n">
         <v>1.8</v>
       </c>
       <c r="D4" t="n">
-        <v>1.133333333333333</v>
+        <v>5.466666666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6666666666666667</v>
+        <v>-3.666666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2272727272727273</v>
+        <v>-0.5045871559633028</v>
       </c>
       <c r="G4" t="n">
-        <v>61.36363636363637</v>
+        <v>24.77064220183486</v>
       </c>
       <c r="H4" t="n">
-        <v>61.36363636363637</v>
+        <v>24.77064220183486</v>
       </c>
       <c r="I4" t="n">
-        <v>38.63636363636364</v>
+        <v>75.22935779816514</v>
       </c>
       <c r="J4" t="n">
         <v>14.95214809962441</v>
@@ -7360,24 +7364,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5.433333333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>4.266666666666667</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6464646464646465</v>
+      </c>
+      <c r="G5" t="n">
+        <v>82.32323232323233</v>
+      </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>82.32323232323233</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>17.67676767676768</v>
       </c>
       <c r="J5" t="n">
         <v>18.35372985587381</v>
@@ -7489,28 +7497,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.933333333333333</v>
+        <v>13.23333333333333</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>6.633333333333334</v>
       </c>
       <c r="D6" t="n">
-        <v>3.933333333333333</v>
+        <v>6.6</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.933333333333333</v>
+        <v>0.0333333333333341</v>
       </c>
       <c r="F6" t="n">
-        <v>-1</v>
+        <v>0.002518891687657489</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>50.12594458438288</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>50.12594458438288</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>49.87405541561713</v>
       </c>
       <c r="J6" t="n">
         <v>9.297854777713539</v>
@@ -7622,28 +7630,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.366666666666667</v>
+        <v>6.866666666666666</v>
       </c>
       <c r="C7" t="n">
-        <v>3.366666666666667</v>
+        <v>5.533333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="E7" t="n">
-        <v>3.366666666666667</v>
+        <v>4.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.6116504854368933</v>
       </c>
       <c r="G7" t="n">
-        <v>100</v>
+        <v>80.58252427184468</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>80.58252427184468</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>19.41747572815534</v>
       </c>
       <c r="J7" t="n">
         <v>21.53425412628779</v>
@@ -7755,28 +7763,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.266666666666667</v>
+        <v>15.4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5.233333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>3.266666666666667</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7333333333333334</v>
+        <v>-4.933333333333333</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1009174311926606</v>
+        <v>-0.3203463203463203</v>
       </c>
       <c r="G8" t="n">
-        <v>55.04587155963303</v>
+        <v>33.98268398268399</v>
       </c>
       <c r="H8" t="n">
-        <v>55.04587155963303</v>
+        <v>33.98268398268399</v>
       </c>
       <c r="I8" t="n">
-        <v>44.95412844036697</v>
+        <v>66.01731601731602</v>
       </c>
       <c r="J8" t="n">
         <v>8.561719896313079</v>
@@ -8017,21 +8025,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.266666666666667</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>2.266666666666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -8275,28 +8287,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2</v>
+        <v>-6.533333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>-1</v>
+        <v>-0.7424242424242423</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>12.87878787878788</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>12.87878787878788</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>87.12121212121212</v>
       </c>
       <c r="J12" t="n">
         <v>12.13663425434414</v>
@@ -8408,24 +8420,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+        <v>-4.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
         <v>7.865896716733953</v>
@@ -8537,28 +8553,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.433333333333333</v>
+        <v>8.466666666666667</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.433333333333333</v>
+        <v>7.066666666666666</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.433333333333333</v>
+        <v>-5.666666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>-1</v>
+        <v>-0.6692913385826771</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>16.53543307086614</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>16.53543307086614</v>
       </c>
       <c r="I14" t="n">
-        <v>100</v>
+        <v>83.46456692913385</v>
       </c>
       <c r="J14" t="n">
         <v>6.099839516651791</v>
@@ -8670,24 +8686,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+        <v>-2.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" t="n">
         <v>9.592764726679457</v>
@@ -8799,16 +8819,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.266666666666667</v>
+        <v>7.233333333333333</v>
       </c>
       <c r="C16" t="n">
-        <v>2.266666666666667</v>
+        <v>7.233333333333333</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>2.266666666666667</v>
+        <v>7.233333333333333</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -8932,16 +8952,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.6</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="C17" t="n">
-        <v>3.6</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6</v>
+        <v>3.766666666666667</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -9065,16 +9085,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.233333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>1.233333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.233333333333333</v>
+        <v>10.86666666666667</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -9460,21 +9480,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+        <v>1.166666666666667</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>100</v>
+      </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -9589,24 +9613,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+        <v>-4.6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" t="n">
         <v>8.292251254506406</v>
@@ -9718,16 +9746,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.266666666666667</v>
+        <v>6.2</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>3.266666666666667</v>
+        <v>6.2</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.266666666666667</v>
+        <v>-6.2</v>
       </c>
       <c r="F23" t="n">
         <v>-1</v>
@@ -9851,25 +9879,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3666666666666666</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="C24" t="n">
-        <v>0.3666666666666666</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3666666666666666</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>99.99999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -10113,28 +10141,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.566666666666667</v>
+        <v>14.1</v>
       </c>
       <c r="C26" t="n">
-        <v>1.566666666666667</v>
+        <v>10.26666666666667</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="E26" t="n">
-        <v>1.566666666666667</v>
+        <v>6.433333333333334</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>0.4562647754137116</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>72.81323877068559</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>72.81323877068559</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>27.18676122931442</v>
       </c>
       <c r="J26" t="n">
         <v>13.17368457267755</v>
@@ -10246,21 +10274,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+        <v>3.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>100</v>
+      </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -10375,28 +10407,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.8</v>
+        <v>7.066666666666666</v>
       </c>
       <c r="C28" t="n">
-        <v>1.3</v>
+        <v>3.566666666666667</v>
       </c>
       <c r="D28" t="n">
         <v>3.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.2</v>
+        <v>0.06666666666666687</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4583333333333334</v>
+        <v>0.009433962264150973</v>
       </c>
       <c r="G28" t="n">
-        <v>27.08333333333334</v>
+        <v>50.47169811320755</v>
       </c>
       <c r="H28" t="n">
-        <v>27.08333333333334</v>
+        <v>50.47169811320755</v>
       </c>
       <c r="I28" t="n">
-        <v>72.91666666666667</v>
+        <v>49.52830188679246</v>
       </c>
       <c r="J28" t="n">
         <v>8.40265745329897</v>
@@ -10508,28 +10540,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.966666666666667</v>
+        <v>6.8</v>
       </c>
       <c r="C29" t="n">
         <v>1.466666666666667</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.03333333333333344</v>
+        <v>-3.866666666666666</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.01123595505617981</v>
+        <v>-0.5686274509803921</v>
       </c>
       <c r="G29" t="n">
-        <v>49.43820224719101</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="H29" t="n">
-        <v>49.43820224719101</v>
+        <v>21.56862745098039</v>
       </c>
       <c r="I29" t="n">
-        <v>50.56179775280899</v>
+        <v>78.4313725490196</v>
       </c>
       <c r="J29" t="n">
         <v>5.648635190581776</v>
@@ -10641,28 +10673,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.433333333333333</v>
+        <v>15.36666666666667</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>5.433333333333334</v>
       </c>
       <c r="D30" t="n">
-        <v>2.433333333333333</v>
+        <v>9.933333333333334</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.433333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-1</v>
+        <v>-0.2928416485900217</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>35.35791757049892</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>35.35791757049892</v>
       </c>
       <c r="I30" t="n">
-        <v>100</v>
+        <v>64.64208242950109</v>
       </c>
       <c r="J30" t="n">
         <v>7.717095652032818</v>
@@ -10903,28 +10935,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="C32" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="G32" t="n">
-        <v>100</v>
+        <v>62.50000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>62.50000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J32" t="n">
         <v>6.197206656395826</v>
@@ -11036,28 +11068,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.966666666666667</v>
+        <v>13.13333333333333</v>
       </c>
       <c r="C33" t="n">
-        <v>2.966666666666667</v>
+        <v>11.13333333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.966666666666667</v>
+        <v>9.133333333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.6954314720812182</v>
       </c>
       <c r="G33" t="n">
-        <v>100</v>
+        <v>84.7715736040609</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>84.7715736040609</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>15.22842639593909</v>
       </c>
       <c r="J33" t="n">
         <v>5.283389429954895</v>
@@ -11169,28 +11201,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.7</v>
+        <v>8.5</v>
       </c>
       <c r="C34" t="n">
-        <v>3.7</v>
+        <v>4.866666666666666</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3.633333333333333</v>
       </c>
       <c r="E34" t="n">
-        <v>3.7</v>
+        <v>1.233333333333333</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0.1450980392156862</v>
       </c>
       <c r="G34" t="n">
-        <v>100</v>
+        <v>57.25490196078431</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>57.25490196078431</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>42.74509803921568</v>
       </c>
       <c r="J34" t="n">
         <v>6.402128777039643</v>
@@ -11302,28 +11334,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4.9</v>
+        <v>18.6</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="D35" t="n">
-        <v>4.9</v>
+        <v>6.9</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.9</v>
+        <v>4.799999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-1</v>
+        <v>0.2580645161290322</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>62.90322580645161</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>62.90322580645161</v>
       </c>
       <c r="I35" t="n">
-        <v>100</v>
+        <v>37.09677419354838</v>
       </c>
       <c r="J35" t="n">
         <v>9.035633476012716</v>
@@ -11435,24 +11467,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>2.233333333333333</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+        <v>-0.03333333333333321</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.0149253731343283</v>
+      </c>
+      <c r="G36" t="n">
+        <v>49.25373134328359</v>
+      </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>49.25373134328359</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>50.74626865671642</v>
       </c>
       <c r="J36" t="n">
         <v>12.65299085548238</v>
@@ -11564,28 +11600,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6.666666666666667</v>
+        <v>15.53333333333333</v>
       </c>
       <c r="C37" t="n">
-        <v>3.066666666666667</v>
+        <v>5.633333333333334</v>
       </c>
       <c r="D37" t="n">
-        <v>3.6</v>
+        <v>9.9</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.5333333333333332</v>
+        <v>-4.266666666666667</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.07999999999999997</v>
+        <v>-0.2746781115879828</v>
       </c>
       <c r="G37" t="n">
-        <v>46</v>
+        <v>36.26609442060086</v>
       </c>
       <c r="H37" t="n">
-        <v>46</v>
+        <v>36.26609442060086</v>
       </c>
       <c r="I37" t="n">
-        <v>54</v>
+        <v>63.73390557939914</v>
       </c>
       <c r="J37" t="n">
         <v>11.92176955359562</v>
@@ -11697,28 +11733,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>8.4</v>
+        <v>13.8</v>
       </c>
       <c r="C38" t="n">
-        <v>5.266666666666667</v>
+        <v>7.866666666666666</v>
       </c>
       <c r="D38" t="n">
-        <v>3.133333333333333</v>
+        <v>5.933333333333334</v>
       </c>
       <c r="E38" t="n">
-        <v>2.133333333333333</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="F38" t="n">
-        <v>0.253968253968254</v>
+        <v>0.1400966183574879</v>
       </c>
       <c r="G38" t="n">
-        <v>62.69841269841269</v>
+        <v>57.00483091787439</v>
       </c>
       <c r="H38" t="n">
-        <v>62.69841269841269</v>
+        <v>57.00483091787439</v>
       </c>
       <c r="I38" t="n">
-        <v>37.3015873015873</v>
+        <v>42.99516908212561</v>
       </c>
       <c r="J38" t="n">
         <v>5.736884095149595</v>
@@ -11830,28 +11866,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.46666666666667</v>
+        <v>23.2</v>
       </c>
       <c r="C39" t="n">
-        <v>14.43333333333333</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="D39" t="n">
-        <v>3.033333333333333</v>
+        <v>5.533333333333333</v>
       </c>
       <c r="E39" t="n">
-        <v>11.4</v>
+        <v>12.13333333333333</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6526717557251909</v>
+        <v>0.5229885057471265</v>
       </c>
       <c r="G39" t="n">
-        <v>82.63358778625954</v>
+        <v>76.14942528735632</v>
       </c>
       <c r="H39" t="n">
-        <v>82.63358778625954</v>
+        <v>76.14942528735632</v>
       </c>
       <c r="I39" t="n">
-        <v>17.36641221374046</v>
+        <v>23.85057471264368</v>
       </c>
       <c r="J39" t="n">
         <v>10.95629570056112</v>
@@ -12092,24 +12128,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+        <v>-1.9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" t="n">
         <v>7.549191710505792</v>
@@ -12221,16 +12261,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.366666666666667</v>
+        <v>3.433333333333333</v>
       </c>
       <c r="C42" t="n">
-        <v>3.366666666666667</v>
+        <v>3.433333333333333</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>3.366666666666667</v>
+        <v>3.433333333333333</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -12354,24 +12394,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>50</v>
+      </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J43" t="n">
         <v>10.35005379231422</v>
@@ -12612,21 +12656,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>100</v>
+      </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -12741,24 +12789,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2.433333333333333</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+        <v>0.2333333333333332</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.09589041095890405</v>
+      </c>
+      <c r="G46" t="n">
+        <v>54.7945205479452</v>
+      </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>54.7945205479452</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>45.2054794520548</v>
       </c>
       <c r="J46" t="n">
         <v>7.436677911206508</v>
@@ -12870,21 +12922,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>100</v>
+      </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -12999,24 +13055,28 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>24.13333333333333</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>20.03333333333333</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+        <v>15.93333333333334</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.6602209944751383</v>
+      </c>
+      <c r="G48" t="n">
+        <v>83.01104972375691</v>
+      </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>83.01104972375691</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>16.98895027624309</v>
       </c>
       <c r="J48" t="n">
         <v>12.15732518307156</v>
@@ -13128,16 +13188,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4.8</v>
+        <v>12.36666666666667</v>
       </c>
       <c r="C49" t="n">
-        <v>4.8</v>
+        <v>12.36666666666667</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>4.8</v>
+        <v>12.36666666666667</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -13261,21 +13321,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>100</v>
+      </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -13390,28 +13454,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>4.533333333333333</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1.566666666666667</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>2.966666666666667</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0.4863387978142077</v>
       </c>
       <c r="G51" t="n">
-        <v>100</v>
+        <v>74.31693989071039</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>74.31693989071039</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>25.68306010928962</v>
       </c>
       <c r="J51" t="n">
         <v>9.934520096342418</v>
@@ -13523,24 +13587,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>2.366666666666667</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.07042253521126754</v>
+      </c>
+      <c r="G52" t="n">
+        <v>53.52112676056338</v>
+      </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>53.52112676056338</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>46.47887323943662</v>
       </c>
       <c r="J52" t="n">
         <v>20.65772813482323</v>
@@ -13652,28 +13720,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.233333333333333</v>
+        <v>7.8</v>
       </c>
       <c r="C53" t="n">
-        <v>1.233333333333333</v>
+        <v>4.866666666666666</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2.933333333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>1.233333333333333</v>
+        <v>1.933333333333333</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0.2478632478632478</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>62.39316239316239</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>62.39316239316239</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>37.60683760683761</v>
       </c>
       <c r="J53" t="n">
         <v>10.52737913028601</v>
